--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:28</t>
+    <t xml:space="preserve">2026-09-10 01:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:42</t>
+    <t xml:space="preserve">2026-09-18 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:39</t>
+    <t xml:space="preserve">2026-09-23 15:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:45</t>
+    <t xml:space="preserve">2026-10-05 16:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -924,7 +924,7 @@
         <v>112.4</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>63.2</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="14">
